--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3_task024.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G3_task024.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -251,6 +251,50 @@
         <v>5.2894432480867248</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>235</v>
+      </c>
+      <c r="B4" s="0">
+        <v>72</v>
+      </c>
+      <c r="C4" s="0">
+        <v>235</v>
+      </c>
+      <c r="D4" s="0">
+        <v>92.881326518449413</v>
+      </c>
+      <c r="E4" s="0">
+        <v>478.67000000000002</v>
+      </c>
+      <c r="F4" s="0">
+        <v>153.86715727648877</v>
+      </c>
+      <c r="G4" s="0">
+        <v>8768.0699107991913</v>
+      </c>
+      <c r="H4" s="0">
+        <v>-2151.810747883992</v>
+      </c>
+      <c r="I4" s="0">
+        <v>6.3100000000000005</v>
+      </c>
+      <c r="J4" s="0">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="K4" s="0">
+        <v>2.9100000000000001</v>
+      </c>
+      <c r="L4" s="0">
+        <v>4.085</v>
+      </c>
+      <c r="M4" s="0">
+        <v>235.17378971852614</v>
+      </c>
+      <c r="N4" s="0">
+        <v>5.2873560486947522</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>